--- a/full base.xlsx
+++ b/full base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JuanMeregone\Documents\datalaptops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3866BFBE-D7D2-4149-9393-DBB4F752FB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8AE85C-D0A9-4ABC-B164-AAEDDFE55FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A6C9A883-3F23-4BFD-A0A0-833FB6DF1CB8}"/>
   </bookViews>
@@ -1560,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3BE3939-ED8F-4C12-8744-EEF31595E9A6}">
-  <dimension ref="A1:I176"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
@@ -6615,28 +6615,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-      <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
-      <c r="H175" s="1"/>
-      <c r="I175" s="5"/>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-      <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-      <c r="H176" s="1"/>
-      <c r="I176" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
